--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B920BFDD-5592-4B1D-871A-69F2A98190F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CE14509-DF0F-40C6-BBAC-867CD371AFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{E56BE921-2D8C-4629-8190-932832146C79}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{9F72203A-E91F-4632-B383-D4E6E7A87795}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E568FBE-0894-43C4-A127-51CF925EC8C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2661BCBC-1CDA-4666-912B-072FE499854F}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CE14509-DF0F-40C6-BBAC-867CD371AFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A35DB55-F144-4243-9A10-0FD15B1F0B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{9F72203A-E91F-4632-B383-D4E6E7A87795}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{53DC5DF2-5B98-4579-A49C-D6A6157A0D60}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2661BCBC-1CDA-4666-912B-072FE499854F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C511AA-A8DB-4EAF-8099-077E86F69DDF}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A35DB55-F144-4243-9A10-0FD15B1F0B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAF41951-57CC-4EF1-99C2-78C8F76919E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{53DC5DF2-5B98-4579-A49C-D6A6157A0D60}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{CBBE8F31-A7A1-4633-B5BA-7A8C7A95B241}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C511AA-A8DB-4EAF-8099-077E86F69DDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C4A092-A5E3-4DC1-9428-72C5E885DEAE}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAF41951-57CC-4EF1-99C2-78C8F76919E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61DF1FE7-2F51-4372-AFCB-4707E4B8697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{CBBE8F31-A7A1-4633-B5BA-7A8C7A95B241}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{8BB59B66-0731-4B6B-B443-B4F6CB681D69}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C4A092-A5E3-4DC1-9428-72C5E885DEAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C56A66-FFED-4E9F-A5E5-33F9B4C2DF32}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61DF1FE7-2F51-4372-AFCB-4707E4B8697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5B19EFD-6F4E-448F-8E78-DFE71D8BBAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{8BB59B66-0731-4B6B-B443-B4F6CB681D69}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{64C0B941-FFE5-4DA1-A89E-2A873801B9E9}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C56A66-FFED-4E9F-A5E5-33F9B4C2DF32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36062150-A53F-4C7F-9743-9ACCD69911B6}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5B19EFD-6F4E-448F-8E78-DFE71D8BBAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6287BE77-E00F-47CE-843B-1C998D0726FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{64C0B941-FFE5-4DA1-A89E-2A873801B9E9}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{81A54FA4-A490-4642-9DF3-2C580A8846F3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36062150-A53F-4C7F-9743-9ACCD69911B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBA7CB2-0A27-41E8-9783-A2D236EB75FE}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6287BE77-E00F-47CE-843B-1C998D0726FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B725BCE-FBB2-42CC-8FD4-2400019FD46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{81A54FA4-A490-4642-9DF3-2C580A8846F3}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{409C0685-C2CA-4648-9B75-1709F32C630E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBA7CB2-0A27-41E8-9783-A2D236EB75FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FC7FBC-9628-4BB1-A82A-6793F79545E3}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B725BCE-FBB2-42CC-8FD4-2400019FD46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E37FB12C-FFD5-4FB6-8B0B-22EFE811A7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{409C0685-C2CA-4648-9B75-1709F32C630E}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{BF3FE836-43E4-478F-A885-0878DF8EB5CF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FC7FBC-9628-4BB1-A82A-6793F79545E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C22C7B-55C4-4A0B-BDAB-FCD9E0F66D26}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E37FB12C-FFD5-4FB6-8B0B-22EFE811A7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{048A77A8-0CFD-4D0F-8F87-48923F792172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{BF3FE836-43E4-478F-A885-0878DF8EB5CF}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{02903072-5F00-4A61-ABD1-2E0D94B389BA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C22C7B-55C4-4A0B-BDAB-FCD9E0F66D26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400298F9-5FD8-41C2-8884-C1DED8785B13}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
